--- a/administrative_forms/006_legal_document_access_request_form--administrative_forms.xlsx
+++ b/administrative_forms/006_legal_document_access_request_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'document_type_1',_'label':_'document_1'}</t>
+          <t>document_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'document_type_1', 'label': 'Document 1'}</t>
+          <t>Document 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'document_type_2',_'label':_'document_2'}</t>
+          <t>document_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'document_type_2', 'label': 'Document 2'}</t>
+          <t>Document 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'document_type_3',_'label':_'document_3'}</t>
+          <t>document_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'document_type_3', 'label': 'Document 3'}</t>
+          <t>Document 3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'document_id_1',_'label':_'document_id_1'}</t>
+          <t>document_id_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'document_id_1', 'label': 'Document ID 1'}</t>
+          <t>Document ID 1</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'document_id_2',_'label':_'document_id_2'}</t>
+          <t>document_id_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'document_id_2', 'label': 'Document ID 2'}</t>
+          <t>Document ID 2</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'document_id_3',_'label':_'document_id_3'}</t>
+          <t>document_id_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'document_id_3', 'label': 'Document ID 3'}</t>
+          <t>Document ID 3</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit_1',_'label':_'submit_1'}</t>
+          <t>submit_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'submit_1', 'label': 'Submit 1'}</t>
+          <t>Submit 1</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'submit_2',_'label':_'submit_2'}</t>
+          <t>submit_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'submit_2', 'label': 'Submit 2'}</t>
+          <t>Submit 2</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'submit_3',_'label':_'submit_3'}</t>
+          <t>submit_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'submit_3', 'label': 'Submit 3'}</t>
+          <t>Submit 3</t>
         </is>
       </c>
     </row>
